--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -660,49 +660,49 @@
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 367994억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 367992억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 369874억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 371028억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 368061억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 369187억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 364963억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 366062억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 361262억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 362335억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 358040억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 357929억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352922억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 352811억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 346344억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 346233억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -912,37 +912,37 @@
     <comment ref="U25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7081억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7084억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7972억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7977억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="X25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8865억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 8873억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Y25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9705억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9715억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Z25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8743억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 8753억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AA25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9608억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9618억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="P26" authorId="0" shapeId="0">
@@ -1767,49 +1767,49 @@
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 367994억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 367992억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 369874억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 371028억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 368061억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 369187억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 364963억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 366062억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 361262억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 362335억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 358040억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 357929억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352922억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 352811억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 346344억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 346233억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2184,37 +2184,37 @@
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7081억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7084억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7972억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7977억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8865억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 8873억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9705억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9715억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8743억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 8753억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9608억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9618억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4028,7 +4028,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.9, "op_wape_pct": 3.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5296.46, "rev_act": 5131.76, "op_pred": 905.36, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5280.5, "rev_act": 5162.05, "op_pred": 902.64, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5280.5, "rev_act": 5746.09, "op_pred": 902.64, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5261.21, "rev_act": 5804.14, "op_pred": 899.34, "op_act": 976.25}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.9, "op_wape_pct": 3.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5296.46, "rev_act": 5131.76, "op_pred": 905.36, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5280.52, "rev_act": 5162.05, "op_pred": 902.64, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5280.52, "rev_act": 5746.09, "op_pred": 902.64, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5261.17, "rev_act": 5804.14, "op_pred": 899.33, "op_act": 976.25}]}</t>
         </is>
       </c>
     </row>
@@ -5404,33 +5404,33 @@
         <v>0.166436</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.205937</v>
+        <v>0.205935</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.050903</v>
+        <v>0.050898</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.007212</v>
+        <v>0.010355</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.066291</v>
+        <v>0.06955500000000001</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.022684</v>
+        <v>0.025767</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>-0.018294</v>
+        <v>-0.015373</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>-0.031993</v>
+        <v>-0.035304</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>-0.04113</v>
+        <v>-0.044358</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>-0.051014</v>
+        <v>-0.054168</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5498,7 +5498,7 @@
         <v>0.051772</v>
       </c>
       <c r="Q22" s="24" t="n">
-        <v>0.051773</v>
+        <v>0.051771</v>
       </c>
       <c r="R22" s="25">
         <f>IFERROR(subQ!R8/subQ!R5,"")</f>
@@ -5508,7 +5508,7 @@
         <v>0.051772</v>
       </c>
       <c r="T22" s="24" t="n">
-        <v>0.051772</v>
+        <v>0.051771</v>
       </c>
       <c r="U22" s="24" t="n">
         <v>0.051771</v>
@@ -5524,13 +5524,13 @@
         <v>0.051772</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>0.051773</v>
+        <v>0.051771</v>
       </c>
       <c r="Z22" s="24" t="n">
         <v>0.051772</v>
       </c>
       <c r="AA22" s="24" t="n">
-        <v>0.051771</v>
+        <v>0.051772</v>
       </c>
       <c r="AB22" s="25">
         <f>IFERROR(subQ!AB8/subQ!AB5,"")</f>
@@ -5608,13 +5608,13 @@
         <v/>
       </c>
       <c r="S23" s="24" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="T23" s="24" t="n">
         <v>0.173155</v>
       </c>
-      <c r="T23" s="24" t="n">
-        <v>0.173154</v>
-      </c>
       <c r="U23" s="24" t="n">
-        <v>0.173155</v>
+        <v>0.173156</v>
       </c>
       <c r="V23" s="24" t="n">
         <v>0.173155</v>
@@ -5627,13 +5627,13 @@
         <v>0.173155</v>
       </c>
       <c r="Y23" s="24" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="Z23" s="24" t="n">
         <v>0.173155</v>
       </c>
-      <c r="Z23" s="24" t="n">
-        <v>0.173156</v>
-      </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173154</v>
+        <v>0.173155</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -5793,26 +5793,26 @@
         <v>58.81</v>
       </c>
       <c r="U25" s="29" t="n">
-        <v>51.88</v>
+        <v>51.89</v>
       </c>
       <c r="V25" s="29" t="n">
-        <v>58.4</v>
+        <v>58.44</v>
       </c>
       <c r="W25" s="30">
         <f>subQ!W11</f>
         <v/>
       </c>
       <c r="X25" s="29" t="n">
-        <v>64.95</v>
+        <v>65</v>
       </c>
       <c r="Y25" s="29" t="n">
-        <v>71.09999999999999</v>
+        <v>71.17</v>
       </c>
       <c r="Z25" s="29" t="n">
-        <v>64.05</v>
+        <v>64.12</v>
       </c>
       <c r="AA25" s="29" t="n">
-        <v>70.39</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="AB25" s="30">
         <f>subQ!AB11</f>
@@ -6089,7 +6089,7 @@
         <v>0.230001</v>
       </c>
       <c r="Q28" s="24" t="n">
-        <v>0.230005</v>
+        <v>0.229996</v>
       </c>
       <c r="R28" s="25">
         <f>IFERROR(subQ!R15/subQ!R14,"")</f>
@@ -6099,23 +6099,23 @@
         <v>0.229997</v>
       </c>
       <c r="T28" s="24" t="n">
+        <v>0.230004</v>
+      </c>
+      <c r="U28" s="24" t="n">
         <v>0.230001</v>
       </c>
-      <c r="U28" s="24" t="n">
-        <v>0.230003</v>
-      </c>
       <c r="V28" s="24" t="n">
-        <v>0.230004</v>
+        <v>0.230002</v>
       </c>
       <c r="W28" s="25">
         <f>IFERROR(subQ!W15/subQ!W14,"")</f>
         <v/>
       </c>
       <c r="X28" s="24" t="n">
-        <v>0.230001</v>
+        <v>0.229998</v>
       </c>
       <c r="Y28" s="24" t="n">
-        <v>0.230004</v>
+        <v>0.229997</v>
       </c>
       <c r="Z28" s="24" t="n">
         <v>0.229998</v>
@@ -6371,11 +6371,11 @@
         <v>-0.0036</v>
       </c>
       <c r="Q31" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="30" t="n"/>
       <c r="S31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T31" s="29" t="n">
         <v>1770.92</v>
@@ -6384,20 +6384,20 @@
         <v>0</v>
       </c>
       <c r="V31" s="29" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="W31" s="30" t="n"/>
       <c r="X31" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y31" s="29" t="n">
         <v>1770.92</v>
       </c>
       <c r="Z31" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AA31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AB31" s="30" t="n"/>
     </row>
@@ -6456,11 +6456,11 @@
         <v>-0.0036</v>
       </c>
       <c r="Q32" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R32" s="30" t="n"/>
       <c r="S32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T32" s="29" t="n">
         <v>1770.92</v>
@@ -6469,20 +6469,20 @@
         <v>0</v>
       </c>
       <c r="V32" s="29" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="W32" s="30" t="n"/>
       <c r="X32" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y32" s="29" t="n">
         <v>1770.92</v>
       </c>
       <c r="Z32" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AA32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="30" t="n"/>
     </row>
@@ -6675,29 +6675,29 @@
       </c>
       <c r="R35" s="25" t="n"/>
       <c r="S35" s="24" t="n">
-        <v>0.117681</v>
+        <v>0.117679</v>
       </c>
       <c r="T35" s="24" t="n">
-        <v>-0.117915</v>
+        <v>-0.117612</v>
       </c>
       <c r="U35" s="24" t="n">
-        <v>0.125762</v>
+        <v>0.126089</v>
       </c>
       <c r="V35" s="24" t="n">
-        <v>0.112069</v>
+        <v>0.112323</v>
       </c>
       <c r="W35" s="25" t="n"/>
       <c r="X35" s="24" t="n">
-        <v>0.094754</v>
+        <v>0.094942</v>
       </c>
       <c r="Y35" s="24" t="n">
-        <v>-0.09913</v>
+        <v>-0.099046</v>
       </c>
       <c r="Z35" s="24" t="n">
-        <v>0.098926</v>
+        <v>0.098792</v>
       </c>
       <c r="AA35" s="24" t="n">
-        <v>0.089438</v>
+        <v>0.089327</v>
       </c>
       <c r="AB35" s="25" t="n"/>
     </row>
@@ -7078,26 +7078,26 @@
         <v>0.183083</v>
       </c>
       <c r="T41" s="24" t="n">
-        <v>0.053476</v>
+        <v>0.052807</v>
       </c>
       <c r="U41" s="24" t="n">
-        <v>-0.014327</v>
+        <v>-0.015918</v>
       </c>
       <c r="V41" s="24" t="n">
-        <v>0.014876</v>
+        <v>0.012562</v>
       </c>
       <c r="W41" s="25" t="n"/>
       <c r="X41" s="24" t="n">
-        <v>-0.022879</v>
+        <v>-0.025739</v>
       </c>
       <c r="Y41" s="24" t="n">
-        <v>-0.019987</v>
+        <v>-0.021587</v>
       </c>
       <c r="Z41" s="24" t="n">
-        <v>0.005168</v>
+        <v>0.0055</v>
       </c>
       <c r="AA41" s="24" t="n">
-        <v>0.023779</v>
+        <v>0.025792</v>
       </c>
       <c r="AB41" s="25" t="n"/>
     </row>
@@ -7154,26 +7154,26 @@
         <v>-0.032427</v>
       </c>
       <c r="T42" s="24" t="n">
-        <v>-0.099911</v>
+        <v>-0.100803</v>
       </c>
       <c r="U42" s="24" t="n">
-        <v>-0.145221</v>
+        <v>-0.14614</v>
       </c>
       <c r="V42" s="24" t="n">
         <v>-0.137137</v>
       </c>
       <c r="W42" s="25" t="n"/>
       <c r="X42" s="24" t="n">
-        <v>-0.127568</v>
+        <v>-0.128649</v>
       </c>
       <c r="Y42" s="24" t="n">
-        <v>-0.136769</v>
+        <v>-0.136905</v>
       </c>
       <c r="Z42" s="24" t="n">
-        <v>-0.125806</v>
+        <v>-0.125942</v>
       </c>
       <c r="AA42" s="24" t="n">
-        <v>-0.114849</v>
+        <v>-0.116009</v>
       </c>
       <c r="AB42" s="25" t="n"/>
     </row>
@@ -7351,13 +7351,13 @@
         <v/>
       </c>
       <c r="S44" s="24" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="T44" s="24" t="n">
         <v>0.173155</v>
       </c>
-      <c r="T44" s="24" t="n">
-        <v>0.173154</v>
-      </c>
       <c r="U44" s="24" t="n">
-        <v>0.173155</v>
+        <v>0.173156</v>
       </c>
       <c r="V44" s="24" t="n">
         <v>0.173155</v>
@@ -7370,13 +7370,13 @@
         <v>0.173155</v>
       </c>
       <c r="Y44" s="24" t="n">
+        <v>0.173154</v>
+      </c>
+      <c r="Z44" s="24" t="n">
         <v>0.173155</v>
       </c>
-      <c r="Z44" s="24" t="n">
-        <v>0.173156</v>
-      </c>
       <c r="AA44" s="24" t="n">
-        <v>0.173154</v>
+        <v>0.173155</v>
       </c>
       <c r="AB44" s="25">
         <f>IFERROR(subQ!AB35/subQ!AB34,"")</f>
@@ -27299,7 +27299,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7502.1</v>
+        <v>7507.6</v>
       </c>
     </row>
     <row r="30">
@@ -27319,7 +27319,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.52</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="32">
@@ -27339,7 +27339,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.377</v>
+        <v>0.3773</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AB$1</definedName>
     <definedName name="환율">변수!$C$6:$AB$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AB$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AB$98</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AB$107</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AB$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AB$90</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AB$1</definedName>
@@ -654,55 +654,55 @@
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 356867억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 358261억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 367992억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 374619억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 371028억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 388652억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 369187억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 404975억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 366062억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 426674억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 362335억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 452357억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 357929억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 479871억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 352811억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 507105억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 346233억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 531239억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -900,49 +900,49 @@
     <comment ref="S25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7182억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7186억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="T25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8028억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 8045억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="U25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7084억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 7139억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="V25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 7977억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 8115억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="X25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8873억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9152억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Y25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9715억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 10193억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="Z25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 8753억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 9491억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AA25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 9618억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 10716억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="P26" authorId="0" shapeId="0">
@@ -1761,55 +1761,55 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 356867억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 358261억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 367992억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 374619억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 371028억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 388652억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 369187억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 404975억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 366062억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 426674억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 362335억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 452357억 × 비례계수 0.0670 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 357929억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 479871억 × 비례계수 0.0670 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 352811억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 507105억 × 비례계수 0.0670 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 346233억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 531239억 × 비례계수 0.0670 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2172,49 +2172,49 @@
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7182억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7186억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8028억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 8045억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7084억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 7139억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 7977억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 8115억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8873억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9152억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9715억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 10193억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 8753억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 9491억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 9618억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 10716억 × 2.93% − 총차입금 0억 × 0.00% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -3900,7 +3900,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.9, "op_wape_pct": 3.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 5296.46, "rev_act": 5131.76, "op_pred": 905.36, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5280.52, "rev_act": 5162.05, "op_pred": 902.64, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5280.52, "rev_act": 5746.09, "op_pred": 902.64, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5261.17, "rev_act": 5804.14, "op_pred": 899.33, "op_act": 976.25}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.9, "op_wape_pct": 3.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": true, "note": "동결 2024Q2 이전 실적 1분기(&lt;8) 또는 이후 실측 0분기 → OOS 비교 불가, 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5296.46, "rev_act": 5131.76, "op_pred": 905.36, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5280.52, "rev_act": 5162.05, "op_pred": 902.64, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5280.52, "rev_act": 5746.09, "op_pred": 902.64, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5261.17, "rev_act": 5804.14, "op_pred": 899.33, "op_act": 976.25}]}</t>
         </is>
       </c>
     </row>
@@ -5404,33 +5404,33 @@
         <v>0.166436</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.205935</v>
+        <v>0.210648</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.050898</v>
+        <v>0.069824</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.010355</v>
+        <v>0.058347</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.06955500000000001</v>
+        <v>0.173233</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.025767</v>
+        <v>0.190957</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>-0.015373</v>
+        <v>0.207511</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>-0.035304</v>
+        <v>0.234706</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>-0.044358</v>
+        <v>0.252191</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>-0.054168</v>
+        <v>0.245069</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5524,7 +5524,7 @@
         <v>0.051772</v>
       </c>
       <c r="Y22" s="24" t="n">
-        <v>0.051771</v>
+        <v>0.051772</v>
       </c>
       <c r="Z22" s="24" t="n">
         <v>0.051772</v>
@@ -5608,10 +5608,10 @@
         <v/>
       </c>
       <c r="S23" s="24" t="n">
+        <v>0.173156</v>
+      </c>
+      <c r="T23" s="24" t="n">
         <v>0.173154</v>
-      </c>
-      <c r="T23" s="24" t="n">
-        <v>0.173155</v>
       </c>
       <c r="U23" s="24" t="n">
         <v>0.173156</v>
@@ -5627,7 +5627,7 @@
         <v>0.173155</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173154</v>
+        <v>0.173155</v>
       </c>
       <c r="Z23" s="24" t="n">
         <v>0.173155</v>
@@ -5787,32 +5787,32 @@
         <v/>
       </c>
       <c r="S25" s="29" t="n">
-        <v>52.62</v>
+        <v>52.64</v>
       </c>
       <c r="T25" s="29" t="n">
-        <v>58.81</v>
+        <v>58.94</v>
       </c>
       <c r="U25" s="29" t="n">
-        <v>51.89</v>
+        <v>52.3</v>
       </c>
       <c r="V25" s="29" t="n">
-        <v>58.44</v>
+        <v>59.45</v>
       </c>
       <c r="W25" s="30">
         <f>subQ!W11</f>
         <v/>
       </c>
       <c r="X25" s="29" t="n">
-        <v>65</v>
+        <v>67.05</v>
       </c>
       <c r="Y25" s="29" t="n">
-        <v>71.17</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="Z25" s="29" t="n">
-        <v>64.12</v>
+        <v>69.53</v>
       </c>
       <c r="AA25" s="29" t="n">
-        <v>70.45999999999999</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="AB25" s="30">
         <f>subQ!AB11</f>
@@ -6089,39 +6089,39 @@
         <v>0.230001</v>
       </c>
       <c r="Q28" s="24" t="n">
-        <v>0.229996</v>
+        <v>0.229998</v>
       </c>
       <c r="R28" s="25">
         <f>IFERROR(subQ!R15/subQ!R14,"")</f>
         <v/>
       </c>
       <c r="S28" s="24" t="n">
-        <v>0.229997</v>
+        <v>0.230001</v>
       </c>
       <c r="T28" s="24" t="n">
-        <v>0.230004</v>
+        <v>0.230001</v>
       </c>
       <c r="U28" s="24" t="n">
         <v>0.230001</v>
       </c>
       <c r="V28" s="24" t="n">
-        <v>0.230002</v>
+        <v>0.230001</v>
       </c>
       <c r="W28" s="25">
         <f>IFERROR(subQ!W15/subQ!W14,"")</f>
         <v/>
       </c>
       <c r="X28" s="24" t="n">
-        <v>0.229998</v>
+        <v>0.230003</v>
       </c>
       <c r="Y28" s="24" t="n">
-        <v>0.229997</v>
+        <v>0.230003</v>
       </c>
       <c r="Z28" s="24" t="n">
-        <v>0.229998</v>
+        <v>0.230003</v>
       </c>
       <c r="AA28" s="24" t="n">
-        <v>0.230002</v>
+        <v>0.230004</v>
       </c>
       <c r="AB28" s="25">
         <f>IFERROR(subQ!AB15/subQ!AB14,"")</f>
@@ -6378,23 +6378,23 @@
         <v>0</v>
       </c>
       <c r="T31" s="29" t="n">
-        <v>1770.92</v>
+        <v>1770.93</v>
       </c>
       <c r="U31" s="29" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="W31" s="30" t="n"/>
       <c r="X31" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y31" s="29" t="n">
-        <v>1770.92</v>
+        <v>1770.91</v>
       </c>
       <c r="Z31" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="29" t="n">
         <v>0</v>
@@ -6463,23 +6463,23 @@
         <v>0</v>
       </c>
       <c r="T32" s="29" t="n">
-        <v>1770.92</v>
+        <v>1770.93</v>
       </c>
       <c r="U32" s="29" t="n">
         <v>0</v>
       </c>
       <c r="V32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="W32" s="30" t="n"/>
       <c r="X32" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y32" s="29" t="n">
-        <v>1770.92</v>
+        <v>1770.91</v>
       </c>
       <c r="Z32" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="29" t="n">
         <v>0</v>
@@ -6671,33 +6671,33 @@
         <v>0.150977</v>
       </c>
       <c r="Q35" s="24" t="n">
-        <v>0.136961</v>
+        <v>0.137476</v>
       </c>
       <c r="R35" s="25" t="n"/>
       <c r="S35" s="24" t="n">
-        <v>0.117679</v>
+        <v>0.119647</v>
       </c>
       <c r="T35" s="24" t="n">
-        <v>-0.117612</v>
+        <v>-0.112725</v>
       </c>
       <c r="U35" s="24" t="n">
-        <v>0.126089</v>
+        <v>0.136753</v>
       </c>
       <c r="V35" s="24" t="n">
-        <v>0.112323</v>
+        <v>0.12788</v>
       </c>
       <c r="W35" s="25" t="n"/>
       <c r="X35" s="24" t="n">
-        <v>0.094942</v>
+        <v>0.113731</v>
       </c>
       <c r="Y35" s="24" t="n">
-        <v>-0.099046</v>
+        <v>-0.068925</v>
       </c>
       <c r="Z35" s="24" t="n">
-        <v>0.098792</v>
+        <v>0.129138</v>
       </c>
       <c r="AA35" s="24" t="n">
-        <v>0.089327</v>
+        <v>0.120897</v>
       </c>
       <c r="AB35" s="25" t="n"/>
     </row>
@@ -7071,33 +7071,33 @@
         <v>-0.07098500000000001</v>
       </c>
       <c r="Q41" s="24" t="n">
-        <v>-0.148607</v>
+        <v>-0.149451</v>
       </c>
       <c r="R41" s="25" t="n"/>
       <c r="S41" s="24" t="n">
-        <v>0.183083</v>
+        <v>0.177068</v>
       </c>
       <c r="T41" s="24" t="n">
-        <v>0.052807</v>
+        <v>0.036096</v>
       </c>
       <c r="U41" s="24" t="n">
-        <v>-0.015918</v>
+        <v>-0.054123</v>
       </c>
       <c r="V41" s="24" t="n">
-        <v>0.012562</v>
+        <v>-0.061218</v>
       </c>
       <c r="W41" s="25" t="n"/>
       <c r="X41" s="24" t="n">
-        <v>-0.025739</v>
+        <v>-0.135739</v>
       </c>
       <c r="Y41" s="24" t="n">
-        <v>-0.021587</v>
+        <v>-0.170323</v>
       </c>
       <c r="Z41" s="24" t="n">
-        <v>0.0055</v>
+        <v>-0.183777</v>
       </c>
       <c r="AA41" s="24" t="n">
-        <v>0.025792</v>
+        <v>-0.192809</v>
       </c>
       <c r="AB41" s="25" t="n"/>
     </row>
@@ -7151,29 +7151,29 @@
       </c>
       <c r="R42" s="25" t="n"/>
       <c r="S42" s="24" t="n">
-        <v>-0.032427</v>
+        <v>-0.033473</v>
       </c>
       <c r="T42" s="24" t="n">
-        <v>-0.100803</v>
+        <v>-0.105263</v>
       </c>
       <c r="U42" s="24" t="n">
-        <v>-0.14614</v>
+        <v>-0.15625</v>
       </c>
       <c r="V42" s="24" t="n">
-        <v>-0.137137</v>
+        <v>-0.156156</v>
       </c>
       <c r="W42" s="25" t="n"/>
       <c r="X42" s="24" t="n">
-        <v>-0.128649</v>
+        <v>-0.158009</v>
       </c>
       <c r="Y42" s="24" t="n">
-        <v>-0.136905</v>
+        <v>-0.182453</v>
       </c>
       <c r="Z42" s="24" t="n">
-        <v>-0.125942</v>
+        <v>-0.184096</v>
       </c>
       <c r="AA42" s="24" t="n">
-        <v>-0.116009</v>
+        <v>-0.185053</v>
       </c>
       <c r="AB42" s="25" t="n"/>
     </row>
@@ -7351,10 +7351,10 @@
         <v/>
       </c>
       <c r="S44" s="24" t="n">
+        <v>0.173156</v>
+      </c>
+      <c r="T44" s="24" t="n">
         <v>0.173154</v>
-      </c>
-      <c r="T44" s="24" t="n">
-        <v>0.173155</v>
       </c>
       <c r="U44" s="24" t="n">
         <v>0.173156</v>
@@ -7370,7 +7370,7 @@
         <v>0.173155</v>
       </c>
       <c r="Y44" s="24" t="n">
-        <v>0.173154</v>
+        <v>0.173155</v>
       </c>
       <c r="Z44" s="24" t="n">
         <v>0.173155</v>
@@ -7832,7 +7832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB98"/>
+  <dimension ref="A1:AB107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -12445,39 +12445,30 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>48975.94</v>
-      </c>
-      <c r="F85" s="18" t="n">
-        <v>80886.64</v>
-      </c>
-      <c r="G85" s="18" t="n">
-        <v>37322.58</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="18" t="n">
-        <v>98176.78999999999</v>
+        <v>4504.18</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>57778.41</v>
+        <v>3748.16</v>
       </c>
       <c r="K85" s="18" t="n">
-        <v>83213.62</v>
+        <v>3717.53</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>84958.92999999999</v>
+        <v>3971.72</v>
       </c>
       <c r="M85" s="34" t="n">
-        <v>324127.75</v>
+        <v>15941.59</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>45323.72</v>
+        <v>4317.85</v>
       </c>
       <c r="O85" s="19" t="n">
-        <v>68374.59</v>
+        <v>4126.78</v>
       </c>
       <c r="P85" s="10" t="n"/>
       <c r="Q85" s="10" t="n"/>
@@ -12499,39 +12490,30 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>1757.68</v>
-      </c>
-      <c r="F86" s="18" t="n">
-        <v>2957.29</v>
-      </c>
-      <c r="G86" s="18" t="n">
-        <v>2880.29</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="18" t="n">
-        <v>5712.82</v>
+        <v>283.67</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>3420.95</v>
+        <v>288.03</v>
       </c>
       <c r="K86" s="18" t="n">
-        <v>3062.74</v>
+        <v>253.42</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>4949.73</v>
+        <v>235.19</v>
       </c>
       <c r="M86" s="34" t="n">
-        <v>17146.24</v>
+        <v>1060.31</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>3301.24</v>
+        <v>244.72</v>
       </c>
       <c r="O86" s="19" t="n">
-        <v>5091.02</v>
+        <v>388.31</v>
       </c>
       <c r="P86" s="10" t="n"/>
       <c r="Q86" s="10" t="n"/>
@@ -12553,39 +12535,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>-1604.86</v>
-      </c>
-      <c r="F87" s="18" t="n">
-        <v>-357.88</v>
-      </c>
-      <c r="G87" s="18" t="n">
-        <v>-463.1</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="H87" s="9" t="n"/>
       <c r="I87" s="18" t="n">
-        <v>-283.2</v>
+        <v>9396.469999999999</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>-287.58</v>
+        <v>13149.5</v>
       </c>
       <c r="K87" s="18" t="n">
-        <v>-252.97</v>
+        <v>9674.16</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>-234.86</v>
+        <v>18271.09</v>
       </c>
       <c r="M87" s="34" t="n">
-        <v>-1058.61</v>
+        <v>50491.22</v>
       </c>
       <c r="N87" s="18" t="n">
-        <v>-244.23</v>
+        <v>36494.26</v>
       </c>
       <c r="O87" s="19" t="n">
-        <v>-385.24</v>
+        <v>27247.3</v>
       </c>
       <c r="P87" s="10" t="n"/>
       <c r="Q87" s="10" t="n"/>
@@ -12607,39 +12580,30 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>-27169.56</v>
-      </c>
-      <c r="F88" s="18" t="n">
-        <v>-27556.01</v>
-      </c>
-      <c r="G88" s="18" t="n">
-        <v>-599.8200000000001</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="H88" s="9" t="n"/>
       <c r="I88" s="18" t="n">
-        <v>-13619.73</v>
+        <v>12027.59</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-17117.81</v>
+        <v>24655.56</v>
       </c>
       <c r="K88" s="18" t="n">
-        <v>-17933.43</v>
+        <v>6372.05</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-17646.7</v>
+        <v>11599.55</v>
       </c>
       <c r="M88" s="34" t="n">
-        <v>-66317.67</v>
+        <v>54654.75</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>-20733.94</v>
+        <v>19419.61</v>
       </c>
       <c r="O88" s="19" t="n">
-        <v>-27277.39</v>
+        <v>16857.99</v>
       </c>
       <c r="P88" s="10" t="n"/>
       <c r="Q88" s="10" t="n"/>
@@ -12661,39 +12625,30 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="n">
-        <v>-129530.4</v>
-      </c>
-      <c r="F89" s="18" t="n">
-        <v>-130593.67</v>
-      </c>
-      <c r="G89" s="18" t="n">
-        <v>66259.99000000001</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="H89" s="9" t="n"/>
       <c r="I89" s="18" t="n">
-        <v>61238.08</v>
+        <v>1865.6</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>-83764.12</v>
+        <v>-800.12</v>
       </c>
       <c r="K89" s="18" t="n">
-        <v>37256.68</v>
+        <v>1063.88</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>-36051.79</v>
+        <v>31.38</v>
       </c>
       <c r="M89" s="34" t="n">
-        <v>-21321.15</v>
+        <v>2160.74</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>6632.48</v>
+        <v>7231.88</v>
       </c>
       <c r="O89" s="19" t="n">
-        <v>82124.3</v>
+        <v>934.97</v>
       </c>
       <c r="P89" s="10" t="n"/>
       <c r="Q89" s="10" t="n"/>
@@ -12715,39 +12670,30 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E90" s="18" t="n">
-        <v>2582.99</v>
-      </c>
-      <c r="F90" s="18" t="n">
-        <v>2598.18</v>
-      </c>
-      <c r="G90" s="18" t="n">
-        <v>2476.77</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="H90" s="9" t="n"/>
       <c r="I90" s="18" t="n">
-        <v>3733.33</v>
+        <v>1037.71</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>5639.96</v>
+        <v>4765.15</v>
       </c>
       <c r="K90" s="18" t="n">
-        <v>2015.11</v>
+        <v>-3873.49</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>5773.13</v>
+        <v>2972.15</v>
       </c>
       <c r="M90" s="34" t="n">
-        <v>17161.53</v>
+        <v>4901.52</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>4087</v>
+        <v>1416.18</v>
       </c>
       <c r="O90" s="19" t="n">
-        <v>2395.59</v>
+        <v>2421.5</v>
       </c>
       <c r="P90" s="10" t="n"/>
       <c r="Q90" s="10" t="n"/>
@@ -12769,39 +12715,30 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E91" s="18" t="n">
-        <v>2582.99</v>
-      </c>
-      <c r="F91" s="18" t="n">
-        <v>2598.18</v>
-      </c>
-      <c r="G91" s="18" t="n">
-        <v>2841.47</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="H91" s="9" t="n"/>
       <c r="I91" s="18" t="n">
-        <v>3733.33</v>
+        <v>16.89</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>5639.96</v>
+        <v>-16.89</v>
       </c>
       <c r="K91" s="18" t="n">
-        <v>2869.32</v>
+        <v>0</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>5773.13</v>
+        <v>13.74</v>
       </c>
       <c r="M91" s="34" t="n">
-        <v>18015.74</v>
+        <v>13.74</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>4087</v>
+        <v>559.73</v>
       </c>
       <c r="O91" s="19" t="n">
-        <v>2395.59</v>
+        <v>166.36</v>
       </c>
       <c r="P91" s="10" t="n"/>
       <c r="Q91" s="10" t="n"/>
@@ -12823,39 +12760,30 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>222645.97</v>
-      </c>
-      <c r="F92" s="18" t="n">
-        <v>-47600.29</v>
-      </c>
-      <c r="G92" s="18" t="n">
-        <v>-29541.57</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="H92" s="9" t="n"/>
       <c r="I92" s="18" t="n">
-        <v>-2004.31</v>
+        <v>4220.51</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>-151633.73</v>
+        <v>3460.13</v>
       </c>
       <c r="K92" s="18" t="n">
-        <v>-36248.22</v>
+        <v>3464.11</v>
       </c>
       <c r="L92" s="18" t="n">
-        <v>-33365.41</v>
+        <v>3736.53</v>
       </c>
       <c r="M92" s="34" t="n">
-        <v>-223251.67</v>
+        <v>14881.28</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>-2009.1</v>
+        <v>4073.13</v>
       </c>
       <c r="O92" s="19" t="n">
-        <v>-125996.3</v>
+        <v>3738.47</v>
       </c>
       <c r="P92" s="10" t="n"/>
       <c r="Q92" s="10" t="n"/>
@@ -12877,39 +12805,25 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
-        </is>
-      </c>
-      <c r="E93" s="18" t="n">
-        <v>1928.5</v>
-      </c>
-      <c r="F93" s="18" t="n">
-        <v>1954.2</v>
-      </c>
-      <c r="G93" s="18" t="n">
-        <v>1926.62</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="H93" s="9" t="n"/>
-      <c r="I93" s="18" t="n">
-        <v>2002.36</v>
-      </c>
       <c r="J93" s="18" t="n">
-        <v>2070.3</v>
+        <v>154.89</v>
       </c>
       <c r="K93" s="18" t="n">
-        <v>2011.89</v>
+        <v>-94.39</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>2091.22</v>
-      </c>
-      <c r="M93" s="34" t="n">
-        <v>8175.77</v>
-      </c>
+        <v>66.51000000000001</v>
+      </c>
+      <c r="M93" s="9" t="n"/>
       <c r="N93" s="18" t="n">
-        <v>2114.11</v>
+        <v>39.71</v>
       </c>
       <c r="O93" s="19" t="n">
-        <v>2706.97</v>
+        <v>-8.49</v>
       </c>
       <c r="P93" s="10" t="n"/>
       <c r="Q93" s="10" t="n"/>
@@ -12931,36 +12845,39 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>143040.25</v>
+        <v>48975.94</v>
       </c>
       <c r="F94" s="18" t="n">
-        <v>-98723.36</v>
+        <v>80886.64</v>
+      </c>
+      <c r="G94" s="18" t="n">
+        <v>37322.58</v>
       </c>
       <c r="H94" s="9" t="n"/>
       <c r="I94" s="18" t="n">
-        <v>157303.7</v>
+        <v>98176.78999999999</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>-179991.87</v>
+        <v>57778.41</v>
       </c>
       <c r="K94" s="18" t="n">
-        <v>85532.64</v>
+        <v>83213.62</v>
       </c>
       <c r="L94" s="18" t="n">
-        <v>16613.5</v>
+        <v>84958.92999999999</v>
       </c>
       <c r="M94" s="34" t="n">
-        <v>79457.97</v>
+        <v>324127.75</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>52748.77</v>
+        <v>45323.72</v>
       </c>
       <c r="O94" s="19" t="n">
-        <v>25767.87</v>
+        <v>68374.59</v>
       </c>
       <c r="P94" s="10" t="n"/>
       <c r="Q94" s="10" t="n"/>
@@ -12982,36 +12899,39 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
-        <v>143040.25</v>
+        <v>1757.68</v>
       </c>
       <c r="F95" s="18" t="n">
-        <v>-98723.36</v>
+        <v>2957.29</v>
+      </c>
+      <c r="G95" s="18" t="n">
+        <v>2880.29</v>
       </c>
       <c r="H95" s="9" t="n"/>
       <c r="I95" s="18" t="n">
-        <v>455769.77</v>
+        <v>5712.82</v>
       </c>
       <c r="J95" s="18" t="n">
-        <v>-179991.86</v>
+        <v>3420.95</v>
       </c>
       <c r="K95" s="18" t="n">
-        <v>85532.63</v>
+        <v>3062.74</v>
       </c>
       <c r="L95" s="18" t="n">
-        <v>16613.5</v>
+        <v>4949.73</v>
       </c>
       <c r="M95" s="34" t="n">
-        <v>377924.04</v>
+        <v>17146.24</v>
       </c>
       <c r="N95" s="18" t="n">
-        <v>430672.81</v>
+        <v>3301.24</v>
       </c>
       <c r="O95" s="19" t="n">
-        <v>25767.87</v>
+        <v>5091.02</v>
       </c>
       <c r="P95" s="10" t="n"/>
       <c r="Q95" s="10" t="n"/>
@@ -13033,28 +12953,39 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>-1604.86</v>
       </c>
       <c r="F96" s="18" t="n">
-        <v>0</v>
+        <v>-357.88</v>
       </c>
       <c r="G96" s="18" t="n">
-        <v>0</v>
+        <v>-463.1</v>
       </c>
       <c r="H96" s="9" t="n"/>
+      <c r="I96" s="18" t="n">
+        <v>-283.2</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>-287.58</v>
+      </c>
       <c r="K96" s="18" t="n">
-        <v>104.72</v>
+        <v>-252.97</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="M96" s="9" t="n"/>
+        <v>-234.86</v>
+      </c>
+      <c r="M96" s="34" t="n">
+        <v>-1058.61</v>
+      </c>
       <c r="N96" s="18" t="n">
-        <v>400.77</v>
+        <v>-244.23</v>
       </c>
       <c r="O96" s="19" t="n">
-        <v>0</v>
+        <v>-385.24</v>
       </c>
       <c r="P96" s="10" t="n"/>
       <c r="Q96" s="10" t="n"/>
@@ -13076,24 +13007,40 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>배당금지급</t>
-        </is>
+          <t>법인세납부(CF)</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>-27169.56</v>
       </c>
       <c r="F97" s="18" t="n">
-        <v>20002.5</v>
+        <v>-27556.01</v>
       </c>
       <c r="G97" s="18" t="n">
-        <v>0</v>
+        <v>-599.8200000000001</v>
       </c>
       <c r="H97" s="9" t="n"/>
+      <c r="I97" s="18" t="n">
+        <v>-13619.73</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>-17117.81</v>
+      </c>
       <c r="K97" s="18" t="n">
-        <v>31380.45</v>
+        <v>-17933.43</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>31380.45</v>
-      </c>
-      <c r="M97" s="9" t="n"/>
-      <c r="O97" s="5" t="n"/>
+        <v>-17646.7</v>
+      </c>
+      <c r="M97" s="34" t="n">
+        <v>-66317.67</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>-20733.94</v>
+      </c>
+      <c r="O97" s="19" t="n">
+        <v>-27277.39</v>
+      </c>
       <c r="P97" s="10" t="n"/>
       <c r="Q97" s="10" t="n"/>
       <c r="R97" s="11" t="n"/>
@@ -13114,15 +13061,40 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
+          <t>투자활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>-129530.4</v>
+      </c>
+      <c r="F98" s="18" t="n">
+        <v>-130593.67</v>
+      </c>
+      <c r="G98" s="18" t="n">
+        <v>66259.99000000001</v>
       </c>
       <c r="H98" s="9" t="n"/>
+      <c r="I98" s="18" t="n">
+        <v>61238.08</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>-83764.12</v>
+      </c>
+      <c r="K98" s="18" t="n">
+        <v>37256.68</v>
+      </c>
       <c r="L98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="9" t="n"/>
-      <c r="O98" s="5" t="n"/>
+        <v>-36051.79</v>
+      </c>
+      <c r="M98" s="34" t="n">
+        <v>-21321.15</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>6632.48</v>
+      </c>
+      <c r="O98" s="19" t="n">
+        <v>82124.3</v>
+      </c>
       <c r="P98" s="10" t="n"/>
       <c r="Q98" s="10" t="n"/>
       <c r="R98" s="11" t="n"/>
@@ -13136,6 +13108,434 @@
       <c r="Z98" s="10" t="n"/>
       <c r="AA98" s="10" t="n"/>
       <c r="AB98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>유형자산의증가</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>2582.99</v>
+      </c>
+      <c r="F99" s="18" t="n">
+        <v>2598.18</v>
+      </c>
+      <c r="G99" s="18" t="n">
+        <v>2476.77</v>
+      </c>
+      <c r="H99" s="9" t="n"/>
+      <c r="I99" s="18" t="n">
+        <v>3733.33</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>5639.96</v>
+      </c>
+      <c r="K99" s="18" t="n">
+        <v>2015.11</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>5773.13</v>
+      </c>
+      <c r="M99" s="34" t="n">
+        <v>17161.53</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>4087</v>
+      </c>
+      <c r="O99" s="19" t="n">
+        <v>2395.59</v>
+      </c>
+      <c r="P99" s="10" t="n"/>
+      <c r="Q99" s="10" t="n"/>
+      <c r="R99" s="11" t="n"/>
+      <c r="S99" s="10" t="n"/>
+      <c r="T99" s="10" t="n"/>
+      <c r="U99" s="10" t="n"/>
+      <c r="V99" s="10" t="n"/>
+      <c r="W99" s="11" t="n"/>
+      <c r="X99" s="10" t="n"/>
+      <c r="Y99" s="10" t="n"/>
+      <c r="Z99" s="10" t="n"/>
+      <c r="AA99" s="10" t="n"/>
+      <c r="AB99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>2582.99</v>
+      </c>
+      <c r="F100" s="18" t="n">
+        <v>2598.18</v>
+      </c>
+      <c r="G100" s="18" t="n">
+        <v>2841.47</v>
+      </c>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="18" t="n">
+        <v>3733.33</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>5639.96</v>
+      </c>
+      <c r="K100" s="18" t="n">
+        <v>2869.32</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>5773.13</v>
+      </c>
+      <c r="M100" s="34" t="n">
+        <v>18015.74</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>4087</v>
+      </c>
+      <c r="O100" s="19" t="n">
+        <v>2395.59</v>
+      </c>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="10" t="n"/>
+      <c r="R100" s="11" t="n"/>
+      <c r="S100" s="10" t="n"/>
+      <c r="T100" s="10" t="n"/>
+      <c r="U100" s="10" t="n"/>
+      <c r="V100" s="10" t="n"/>
+      <c r="W100" s="11" t="n"/>
+      <c r="X100" s="10" t="n"/>
+      <c r="Y100" s="10" t="n"/>
+      <c r="Z100" s="10" t="n"/>
+      <c r="AA100" s="10" t="n"/>
+      <c r="AB100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>222645.97</v>
+      </c>
+      <c r="F101" s="18" t="n">
+        <v>-47600.29</v>
+      </c>
+      <c r="G101" s="18" t="n">
+        <v>-29541.57</v>
+      </c>
+      <c r="H101" s="9" t="n"/>
+      <c r="I101" s="18" t="n">
+        <v>-2004.31</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>-151633.73</v>
+      </c>
+      <c r="K101" s="18" t="n">
+        <v>-36248.22</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>-33365.41</v>
+      </c>
+      <c r="M101" s="34" t="n">
+        <v>-223251.67</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>-2009.1</v>
+      </c>
+      <c r="O101" s="19" t="n">
+        <v>-125996.3</v>
+      </c>
+      <c r="P101" s="10" t="n"/>
+      <c r="Q101" s="10" t="n"/>
+      <c r="R101" s="11" t="n"/>
+      <c r="S101" s="10" t="n"/>
+      <c r="T101" s="10" t="n"/>
+      <c r="U101" s="10" t="n"/>
+      <c r="V101" s="10" t="n"/>
+      <c r="W101" s="11" t="n"/>
+      <c r="X101" s="10" t="n"/>
+      <c r="Y101" s="10" t="n"/>
+      <c r="Z101" s="10" t="n"/>
+      <c r="AA101" s="10" t="n"/>
+      <c r="AB101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>1928.5</v>
+      </c>
+      <c r="F102" s="18" t="n">
+        <v>1954.2</v>
+      </c>
+      <c r="G102" s="18" t="n">
+        <v>1926.62</v>
+      </c>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="18" t="n">
+        <v>2002.36</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>2070.3</v>
+      </c>
+      <c r="K102" s="18" t="n">
+        <v>2011.89</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>2091.22</v>
+      </c>
+      <c r="M102" s="34" t="n">
+        <v>8175.77</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>2114.11</v>
+      </c>
+      <c r="O102" s="19" t="n">
+        <v>2706.97</v>
+      </c>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="10" t="n"/>
+      <c r="R102" s="11" t="n"/>
+      <c r="S102" s="10" t="n"/>
+      <c r="T102" s="10" t="n"/>
+      <c r="U102" s="10" t="n"/>
+      <c r="V102" s="10" t="n"/>
+      <c r="W102" s="11" t="n"/>
+      <c r="X102" s="10" t="n"/>
+      <c r="Y102" s="10" t="n"/>
+      <c r="Z102" s="10" t="n"/>
+      <c r="AA102" s="10" t="n"/>
+      <c r="AB102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>143040.25</v>
+      </c>
+      <c r="F103" s="18" t="n">
+        <v>-98723.36</v>
+      </c>
+      <c r="H103" s="9" t="n"/>
+      <c r="I103" s="18" t="n">
+        <v>157303.7</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>-179991.87</v>
+      </c>
+      <c r="K103" s="18" t="n">
+        <v>85532.64</v>
+      </c>
+      <c r="L103" s="18" t="n">
+        <v>16613.5</v>
+      </c>
+      <c r="M103" s="34" t="n">
+        <v>79457.97</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>52748.77</v>
+      </c>
+      <c r="O103" s="19" t="n">
+        <v>25767.87</v>
+      </c>
+      <c r="P103" s="10" t="n"/>
+      <c r="Q103" s="10" t="n"/>
+      <c r="R103" s="11" t="n"/>
+      <c r="S103" s="10" t="n"/>
+      <c r="T103" s="10" t="n"/>
+      <c r="U103" s="10" t="n"/>
+      <c r="V103" s="10" t="n"/>
+      <c r="W103" s="11" t="n"/>
+      <c r="X103" s="10" t="n"/>
+      <c r="Y103" s="10" t="n"/>
+      <c r="Z103" s="10" t="n"/>
+      <c r="AA103" s="10" t="n"/>
+      <c r="AB103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>143040.25</v>
+      </c>
+      <c r="F104" s="18" t="n">
+        <v>-98723.36</v>
+      </c>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="18" t="n">
+        <v>455769.77</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>-179991.86</v>
+      </c>
+      <c r="K104" s="18" t="n">
+        <v>85532.63</v>
+      </c>
+      <c r="L104" s="18" t="n">
+        <v>16613.5</v>
+      </c>
+      <c r="M104" s="34" t="n">
+        <v>377924.04</v>
+      </c>
+      <c r="N104" s="18" t="n">
+        <v>430672.81</v>
+      </c>
+      <c r="O104" s="19" t="n">
+        <v>25767.87</v>
+      </c>
+      <c r="P104" s="10" t="n"/>
+      <c r="Q104" s="10" t="n"/>
+      <c r="R104" s="11" t="n"/>
+      <c r="S104" s="10" t="n"/>
+      <c r="T104" s="10" t="n"/>
+      <c r="U104" s="10" t="n"/>
+      <c r="V104" s="10" t="n"/>
+      <c r="W104" s="11" t="n"/>
+      <c r="X104" s="10" t="n"/>
+      <c r="Y104" s="10" t="n"/>
+      <c r="Z104" s="10" t="n"/>
+      <c r="AA104" s="10" t="n"/>
+      <c r="AB104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>유형자산의감소</t>
+        </is>
+      </c>
+      <c r="F105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="9" t="n"/>
+      <c r="K105" s="18" t="n">
+        <v>104.72</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="M105" s="9" t="n"/>
+      <c r="N105" s="18" t="n">
+        <v>400.77</v>
+      </c>
+      <c r="O105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" s="10" t="n"/>
+      <c r="Q105" s="10" t="n"/>
+      <c r="R105" s="11" t="n"/>
+      <c r="S105" s="10" t="n"/>
+      <c r="T105" s="10" t="n"/>
+      <c r="U105" s="10" t="n"/>
+      <c r="V105" s="10" t="n"/>
+      <c r="W105" s="11" t="n"/>
+      <c r="X105" s="10" t="n"/>
+      <c r="Y105" s="10" t="n"/>
+      <c r="Z105" s="10" t="n"/>
+      <c r="AA105" s="10" t="n"/>
+      <c r="AB105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="F106" s="18" t="n">
+        <v>20002.5</v>
+      </c>
+      <c r="G106" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="9" t="n"/>
+      <c r="K106" s="18" t="n">
+        <v>31380.45</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>31380.45</v>
+      </c>
+      <c r="M106" s="9" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="10" t="n"/>
+      <c r="R106" s="11" t="n"/>
+      <c r="S106" s="10" t="n"/>
+      <c r="T106" s="10" t="n"/>
+      <c r="U106" s="10" t="n"/>
+      <c r="V106" s="10" t="n"/>
+      <c r="W106" s="11" t="n"/>
+      <c r="X106" s="10" t="n"/>
+      <c r="Y106" s="10" t="n"/>
+      <c r="Z106" s="10" t="n"/>
+      <c r="AA106" s="10" t="n"/>
+      <c r="AB106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>무형자산의증가</t>
+        </is>
+      </c>
+      <c r="H107" s="9" t="n"/>
+      <c r="L107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="9" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="10" t="n"/>
+      <c r="Q107" s="10" t="n"/>
+      <c r="R107" s="11" t="n"/>
+      <c r="S107" s="10" t="n"/>
+      <c r="T107" s="10" t="n"/>
+      <c r="U107" s="10" t="n"/>
+      <c r="V107" s="10" t="n"/>
+      <c r="W107" s="11" t="n"/>
+      <c r="X107" s="10" t="n"/>
+      <c r="Y107" s="10" t="n"/>
+      <c r="Z107" s="10" t="n"/>
+      <c r="AA107" s="10" t="n"/>
+      <c r="AB107" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13324,7 +13724,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27299,7 +27699,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7507.6</v>
+        <v>7630.2</v>
       </c>
     </row>
     <row r="30">
@@ -27319,7 +27719,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
@@ -27339,7 +27739,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3773</v>
+        <v>0.3835</v>
       </c>
     </row>
     <row r="34">
@@ -27349,7 +27749,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.19</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="35">
@@ -27359,7 +27759,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>83400</v>
+        <v>84800</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AB$1</definedName>
@@ -663,55 +663,55 @@
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 210631억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 210618억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 218743억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 218715억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226127억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235406억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 235347억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248179억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 248119억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263315억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263257억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279540억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279485억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 295601억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 295549억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 309834억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 309786억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 210631억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 210618억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 218743억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 218715억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226171억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226127억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235406억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235347억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248179억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248119억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263315억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263257억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279540억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279485억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 295601억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 295549억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 309834억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 309786억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2034,31 +2034,31 @@
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8006억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8005억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9015억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9014억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10028억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10027억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9297억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10490억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10489억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2094,31 +2094,31 @@
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8006억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8005억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9015억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9014억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10028억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10027억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9297억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10490억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10489억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>234500</v>
+        <v>225000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>229500</v>
+        <v>220000</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>235750</v>
+        <v>232166.7</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5586,33 +5586,33 @@
         <v>0.134636004</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.189825217</v>
+        <v>0.189751603</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.04423936</v>
+        <v>0.044103615</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.029548105</v>
+        <v>0.029348248</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.171984378</v>
+        <v>0.171692417</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.178261266</v>
+        <v>0.178052482</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.203760152</v>
+        <v>0.203654965</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.235969704</v>
+        <v>0.23596698</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.255705889</v>
+        <v>0.255797455</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.248434048</v>
+        <v>0.248536298</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5793,39 +5793,39 @@
         <v>0.17315566</v>
       </c>
       <c r="Q23" s="24" t="n">
-        <v>0.173155387</v>
+        <v>0.173154703</v>
       </c>
       <c r="R23" s="25">
         <f>IFERROR(subQ!R9/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S23" s="24" t="n">
-        <v>0.173154964</v>
+        <v>0.173154141</v>
       </c>
       <c r="T23" s="24" t="n">
-        <v>0.173154675</v>
+        <v>0.173154818</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173155688</v>
+        <v>0.173154862</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155023</v>
+        <v>0.173154962</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173154587</v>
+        <v>0.173154844</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173154646</v>
+        <v>0.173154791</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.17315455</v>
+        <v>0.173154721</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173154998</v>
+        <v>0.173154542</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>0.001983533</v>
+        <v>0.002343339</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>-0.005213018</v>
+        <v>0.001305005</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>0.001290262</v>
+        <v>-0.00630248</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.919533811</v>
+        <v>1770.915190147</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.003161044</v>
+        <v>-0.005411095</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>0.003611012</v>
+        <v>0.000152792</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>-0.004936943</v>
+        <v>0.00350623</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.919245137</v>
+        <v>1770.911939029</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.003109484</v>
+        <v>0.00071238</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.005796354</v>
+        <v>-0.00529971</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>0.001983533</v>
+        <v>0.002343339</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>-0.005213018</v>
+        <v>0.001305005</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>0.001290262</v>
+        <v>-0.00630248</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.919533811</v>
+        <v>1770.915190147</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.003161044</v>
+        <v>-0.005411095</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>0.003611012</v>
+        <v>0.000152792</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>-0.004936943</v>
+        <v>0.00350623</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.919245137</v>
+        <v>1770.911939029</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.003109484</v>
+        <v>0.00071238</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.005796354</v>
+        <v>-0.00529971</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7013,33 +7013,33 @@
         <v>0.146919578</v>
       </c>
       <c r="Q36" s="24" t="n">
-        <v>0.135571088</v>
+        <v>0.135563145</v>
       </c>
       <c r="R36" s="25" t="n"/>
       <c r="S36" s="24" t="n">
-        <v>0.117407763</v>
+        <v>0.117393196</v>
       </c>
       <c r="T36" s="24" t="n">
-        <v>-0.116464063</v>
+        <v>-0.116485176</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134411726</v>
+        <v>0.134385039</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.126017672</v>
+        <v>0.125997442</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.112329338</v>
+        <v>0.112314528</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.072895101</v>
+        <v>-0.072922246</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.12839963</v>
+        <v>0.128394552</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.120339019</v>
+        <v>0.120335898</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>234500</v>
+        <v>225000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300007224208007</v>
+        <v>0.2300007775152028</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177187390512976</v>
+        <v>0.05177195553979155</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02881964846545134</v>
+        <v>0.02882004362065286</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28742,7 +28742,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7449.1</v>
+        <v>7448.4</v>
       </c>
     </row>
     <row r="30">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>31.48</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.78</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="33">
@@ -28782,7 +28782,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3744</v>
+        <v>0.3743</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 210618억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 210607억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 218715억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 218685억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226127억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226078억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235347억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 235281억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248119억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 248047억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263257억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263188억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279485억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279419억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 295549억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 295486억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 309786억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 309727억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 210618억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 210607억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 218715억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 218685억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226127억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226078억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235347억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235281억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248119억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248047억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263257억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263188억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279485억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279419억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 295549억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 295486억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 309786억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 309727억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -2022,7 +2022,7 @@
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7988억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7987억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2040,25 +2040,25 @@
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9014억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9013억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10027억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10025억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9294억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10489억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10487억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2082,7 +2082,7 @@
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7988억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7987억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -2100,25 +2100,25 @@
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9014억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9013억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10027억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10025억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9294억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10489억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10487억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>220000</v>
+        <v>216500</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>232166.7</v>
+        <v>229500</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5586,33 +5586,33 @@
         <v>0.134636004</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.189751603</v>
+        <v>0.189687675</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.044103615</v>
+        <v>0.043959169</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.029348248</v>
+        <v>0.029127715</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.171692417</v>
+        <v>0.171362671</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.178052482</v>
+        <v>0.177775462</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.203654965</v>
+        <v>0.203504771</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.23596698</v>
+        <v>0.23593886</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.255797455</v>
+        <v>0.255884125</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.248536298</v>
+        <v>0.248662033</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5793,39 +5793,39 @@
         <v>0.17315566</v>
       </c>
       <c r="Q23" s="24" t="n">
-        <v>0.173154703</v>
+        <v>0.173154238</v>
       </c>
       <c r="R23" s="25">
         <f>IFERROR(subQ!R9/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S23" s="24" t="n">
-        <v>0.173154141</v>
+        <v>0.173154761</v>
       </c>
       <c r="T23" s="24" t="n">
-        <v>0.173154818</v>
+        <v>0.173155093</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154862</v>
+        <v>0.173155222</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173154962</v>
+        <v>0.173155223</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173154844</v>
+        <v>0.173154705</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173154791</v>
+        <v>0.173155201</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173154721</v>
+        <v>0.173155321</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173154542</v>
+        <v>0.173155025</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>0.002343339</v>
+        <v>0.001251925</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.001305005</v>
+        <v>-0.006073347</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.00630248</v>
+        <v>-0.00553566</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.915190147</v>
+        <v>1770.923702524</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.005411095</v>
+        <v>-0.00265934</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>0.000152792</v>
+        <v>-0.001695204</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>0.00350623</v>
+        <v>-0.006901615</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.911939029</v>
+        <v>1770.923164395</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>0.00071238</v>
+        <v>-0.007212785</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.00529971</v>
+        <v>0.000603019</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>0.002343339</v>
+        <v>0.001251925</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.001305005</v>
+        <v>-0.006073347</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.00630248</v>
+        <v>-0.00553566</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.915190147</v>
+        <v>1770.923702524</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.005411095</v>
+        <v>-0.00265934</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>0.000152792</v>
+        <v>-0.001695204</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>0.00350623</v>
+        <v>-0.006901615</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.911939029</v>
+        <v>1770.923164395</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>0.00071238</v>
+        <v>-0.007212785</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.00529971</v>
+        <v>0.000603019</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7013,33 +7013,33 @@
         <v>0.146919578</v>
       </c>
       <c r="Q36" s="24" t="n">
-        <v>0.135563145</v>
+        <v>0.135556791</v>
       </c>
       <c r="R36" s="25" t="n"/>
       <c r="S36" s="24" t="n">
-        <v>0.117393196</v>
+        <v>0.117378465</v>
       </c>
       <c r="T36" s="24" t="n">
-        <v>-0.116485176</v>
+        <v>-0.116509899</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134385039</v>
+        <v>0.134355896</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.125997442</v>
+        <v>0.125970343</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.112314528</v>
+        <v>0.112297632</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.072922246</v>
+        <v>-0.072954331</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.128394552</v>
+        <v>0.128385365</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.120335898</v>
+        <v>0.120332556</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>225000</v>
+        <v>220000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 237,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 233,500원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300007775152028</v>
+        <v>0.2300015396120177</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177195553979155</v>
+        <v>0.05177174373914351</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882004362065286</v>
+        <v>0.02881976601690427</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28742,7 +28742,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7448.4</v>
+        <v>7447.7</v>
       </c>
     </row>
     <row r="30">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.21</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.31</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -663,55 +663,55 @@
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 210607억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 210600억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 218685억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 218677억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226078억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 226071억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235281억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 235273억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248047억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 248046억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263188억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 263187억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279419억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 279418억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 295486억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 295485억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 309727억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객지수 4분기 이동합(t−0) 309726억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1650,55 +1650,55 @@
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 210607억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 210600억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 218685억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 218677억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226078억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 226071억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235281억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 235273억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248047억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 248046억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263188억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 263187억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279419억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 279418억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 295486억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 295485억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 309727억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객지수 4분기 이동합(t−0) 309726억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
 [yoy]</t>
       </text>
     </comment>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>216500</v>
+        <v>213500</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>229500</v>
+        <v>227300</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5586,33 +5586,33 @@
         <v>0.134636004</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.189687675</v>
+        <v>0.189646994</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.043959169</v>
+        <v>0.043926103</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.029127715</v>
+        <v>0.029093257</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.171362671</v>
+        <v>0.171324888</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.177775462</v>
+        <v>0.177810852</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.203504771</v>
+        <v>0.20353789</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.23593886</v>
+        <v>0.235975222</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.255884125</v>
+        <v>0.255920238</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.248662033</v>
+        <v>0.248663065</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5793,39 +5793,39 @@
         <v>0.17315566</v>
       </c>
       <c r="Q23" s="24" t="n">
-        <v>0.173154238</v>
+        <v>0.173155274</v>
       </c>
       <c r="R23" s="25">
         <f>IFERROR(subQ!R9/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S23" s="24" t="n">
-        <v>0.173154761</v>
+        <v>0.173155244</v>
       </c>
       <c r="T23" s="24" t="n">
-        <v>0.173155093</v>
+        <v>0.173154194</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173155222</v>
+        <v>0.173154943</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155223</v>
+        <v>0.173154559</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173154705</v>
+        <v>0.173155424</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173155201</v>
+        <v>0.17315455</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155321</v>
+        <v>0.17315476</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155025</v>
+        <v>0.173154493</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>0.001251925</v>
+        <v>0.001329959</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>-0.006073347</v>
+        <v>0.0008929539999999999</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.00553566</v>
+        <v>-0.008771025</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.923702524</v>
+        <v>1770.922574021</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.00265934</v>
+        <v>-0.003829217</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>-0.001695204</v>
+        <v>5.5752e-05</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>-0.006901615</v>
+        <v>-0.007544357</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.923164395</v>
+        <v>1770.914799689</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.007212785</v>
+        <v>0.004442843</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>0.000603019</v>
+        <v>-0.007758947</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>0.001251925</v>
+        <v>0.001329959</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>-0.006073347</v>
+        <v>0.0008929539999999999</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.00553566</v>
+        <v>-0.008771025</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.923702524</v>
+        <v>1770.922574021</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.00265934</v>
+        <v>-0.003829217</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>-0.001695204</v>
+        <v>5.5752e-05</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>-0.006901615</v>
+        <v>-0.007544357</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.923164395</v>
+        <v>1770.914799689</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.007212785</v>
+        <v>0.004442843</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>0.000603019</v>
+        <v>-0.007758947</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7013,33 +7013,33 @@
         <v>0.146919578</v>
       </c>
       <c r="Q36" s="24" t="n">
-        <v>0.135556791</v>
+        <v>0.135552025</v>
       </c>
       <c r="R36" s="25" t="n"/>
       <c r="S36" s="24" t="n">
-        <v>0.117378465</v>
+        <v>0.11737476</v>
       </c>
       <c r="T36" s="24" t="n">
-        <v>-0.116509899</v>
+        <v>-0.116513278</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134355896</v>
+        <v>0.134353168</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.125970343</v>
+        <v>0.125970825</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.112297632</v>
+        <v>0.112299127</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.072954331</v>
+        <v>-0.072956202</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.128385365</v>
+        <v>0.128387161</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.120332556</v>
+        <v>0.120333094</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 233,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 226,500원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300015396120177</v>
+        <v>0.2300012882629816</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177174373914351</v>
+        <v>0.05177160437804391</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02881976601690427</v>
+        <v>0.02881959073766367</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28742,7 +28742,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7447.7</v>
+        <v>7447.5</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AB$1</definedName>
@@ -657,61 +657,61 @@
     <comment ref="P21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 200861억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 45175억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 210600억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 48694억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="S21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 218677억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 52634억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="T21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 226071억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 54819억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 235273억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 55521억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 248046억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 56959억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 263187억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 59908억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 279418억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 63218억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 295485억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 67199억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객지수 4분기 이동합(t−0) 309726억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)</t>
+고객 매출 가중지수(t−3) 71356억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1644,61 +1644,61 @@
   <commentList>
     <comment ref="P5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 200861억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 45175억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 210600억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 48694억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="S5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 218677억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 52634억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="T5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 226071억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 54819억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 235273억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 55521억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 248046억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 56959억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 263187억 × 비례계수 0.1120 × 계절비중 Q1 0.245(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 59908억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 279418억 × 비례계수 0.1120 × 계절비중 Q2 0.236(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 63218억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 295485억 × 비례계수 0.1120 × 계절비중 Q3 0.259(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 67199억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객지수 4분기 이동합(t−0) 309726억 × 비례계수 0.1120 × 계절비중 Q4 0.260(계절비중 — 최근 1개 연도(2026) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.99, n=6, 창 8)
+        <t>추정: 고객 매출 가중지수(t−3) 71356억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2010,55 +2010,55 @@
     </comment>
     <comment ref="Q11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 6295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 6279억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="S11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7148억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7133억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="T11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7987억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8057억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="U11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7057억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 7253억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8005억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8227억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9013억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10025억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9294억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10487억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2070,55 +2070,55 @@
     </comment>
     <comment ref="Q12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 6295억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 6279억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="S12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7148억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7133억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="T12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7987억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8057억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="U12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 7057억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 7253억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8005억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8227억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9013억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10025억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9294억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10487억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -5583,36 +5583,36 @@
         <v/>
       </c>
       <c r="P21" s="24" t="n">
-        <v>0.134636004</v>
+        <v>0.110938482</v>
       </c>
       <c r="Q21" s="24" t="n">
-        <v>0.189646994</v>
+        <v>0.190466435</v>
       </c>
       <c r="R21" s="25" t="n"/>
       <c r="S21" s="24" t="n">
-        <v>0.043926103</v>
+        <v>0.155998897</v>
       </c>
       <c r="T21" s="24" t="n">
-        <v>0.029093257</v>
+        <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.171324888</v>
+        <v>0.22901315</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.177810852</v>
+        <v>0.169719702</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.20353789</v>
+        <v>0.138182032</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.235975222</v>
+        <v>0.15321204</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.255920238</v>
+        <v>0.21034183</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.248663065</v>
+        <v>0.252766332</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5790,42 +5790,42 @@
         <v/>
       </c>
       <c r="P23" s="24" t="n">
-        <v>0.17315566</v>
+        <v>0.173155215</v>
       </c>
       <c r="Q23" s="24" t="n">
-        <v>0.173155274</v>
+        <v>0.173154876</v>
       </c>
       <c r="R23" s="25">
         <f>IFERROR(subQ!R9/subQ!R5,"")</f>
         <v/>
       </c>
       <c r="S23" s="24" t="n">
-        <v>0.173155244</v>
+        <v>0.173155468</v>
       </c>
       <c r="T23" s="24" t="n">
-        <v>0.173154194</v>
+        <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154943</v>
+        <v>0.173154514</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173154559</v>
+        <v>0.173155524</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173155424</v>
+        <v>0.173154911</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.17315455</v>
+        <v>0.173154394</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.17315476</v>
+        <v>0.173155089</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173154493</v>
+        <v>0.173155169</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>0.001329959</v>
+        <v>-0.004177373</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.0008929539999999999</v>
+        <v>0.003790107</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.008771025</v>
+        <v>-0.002624778</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.922574021</v>
+        <v>1770.927891224</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.003829217</v>
+        <v>-0.007557966</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>5.5752e-05</v>
+        <v>-0.004887568</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>-0.007544357</v>
+        <v>0.004248666</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.914799689</v>
+        <v>1770.920259884</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>0.004442843</v>
+        <v>-0.006632587</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.007758947</v>
+        <v>0.005268755</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>0.001329959</v>
+        <v>-0.004177373</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.0008929539999999999</v>
+        <v>0.003790107</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.008771025</v>
+        <v>-0.002624778</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.922574021</v>
+        <v>1770.927891224</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.003829217</v>
+        <v>-0.007557966</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>5.5752e-05</v>
+        <v>-0.004887568</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>-0.007544357</v>
+        <v>0.004248666</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.914799689</v>
+        <v>1770.920259884</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>0.004442843</v>
+        <v>-0.006632587</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.007758947</v>
+        <v>0.005268755</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7010,36 +7010,36 @@
         <v/>
       </c>
       <c r="P36" s="24" t="n">
-        <v>0.146919578</v>
+        <v>0.14396437</v>
       </c>
       <c r="Q36" s="24" t="n">
-        <v>0.135552025</v>
+        <v>0.135978646</v>
       </c>
       <c r="R36" s="25" t="n"/>
       <c r="S36" s="24" t="n">
-        <v>0.11737476</v>
+        <v>0.129660318</v>
       </c>
       <c r="T36" s="24" t="n">
-        <v>-0.116513278</v>
+        <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134353168</v>
+        <v>0.134292182</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.125970825</v>
+        <v>0.121990767</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.112299127</v>
+        <v>0.114705952</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.072956202</v>
+        <v>-0.063220809</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.128387161</v>
+        <v>0.122809839</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.120333094</v>
+        <v>0.116446501</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300012882629816</v>
+        <v>0.2300016484088297</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177160437804391</v>
+        <v>0.05177166530673166</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02881959073766367</v>
+        <v>0.02882056843497378</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28742,7 +28742,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7447.5</v>
+        <v>7885.8</v>
       </c>
     </row>
     <row r="30">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.54</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="32">
@@ -28782,7 +28782,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3743</v>
+        <v>0.3963</v>
       </c>
     </row>
     <row r="34">
@@ -28792,7 +28792,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.16</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="35">
@@ -28802,7 +28802,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>82800</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AB$1</definedName>
@@ -681,37 +681,37 @@
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 55521억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 55519억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 56959억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 56977억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59908억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59925억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63218억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63235억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 67199억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 67215억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71356억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 71372억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 55521억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 55519억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 56959억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 56977억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59908억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59925억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63218억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63235억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 67199억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 67215억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71356억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 71372억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2052,13 +2052,13 @@
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9640억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10824억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2112,13 +2112,13 @@
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9640억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10824억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>220000</v>
+        <v>218000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>227300</v>
+        <v>226900</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.22901315</v>
+        <v>0.228974561</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.169719702</v>
+        <v>0.170089093</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.138182032</v>
+        <v>0.138519256</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.15321204</v>
+        <v>0.153522814</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.21034183</v>
+        <v>0.210675276</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.252766332</v>
+        <v>0.252644813</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154514</v>
+        <v>0.173154242</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155524</v>
+        <v>0.173155098</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173154911</v>
+        <v>0.173155193</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173154394</v>
+        <v>0.173155362</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155089</v>
+        <v>0.173155274</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155169</v>
+        <v>0.173155045</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.004177373</v>
+        <v>-0.003771182</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.003790107</v>
+        <v>0.004227551</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.002624778</v>
+        <v>-0.002152311</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.927891224</v>
+        <v>1770.9283826</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.007557966</v>
+        <v>-0.007858850000000001</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>-0.004887568</v>
+        <v>-0.004243831</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>0.004248666</v>
+        <v>0.006637913</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.920259884</v>
+        <v>1770.91659179</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.006632587</v>
+        <v>0.005997418</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>0.005268755</v>
+        <v>-0.005968823</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.004177373</v>
+        <v>-0.003771182</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.003790107</v>
+        <v>0.004227551</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.002624778</v>
+        <v>-0.002152311</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.927891224</v>
+        <v>1770.9283826</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.007557966</v>
+        <v>-0.007858850000000001</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>-0.004887568</v>
+        <v>-0.004243831</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>0.004248666</v>
+        <v>0.006637913</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.920259884</v>
+        <v>1770.91659179</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.006632587</v>
+        <v>0.005997418</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>0.005268755</v>
+        <v>-0.005968823</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134292182</v>
+        <v>0.134288046</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.121990767</v>
+        <v>0.122028892</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.114705952</v>
+        <v>0.114733889</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.063220809</v>
+        <v>-0.063188153</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122809839</v>
+        <v>0.122826763</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.116446501</v>
+        <v>0.116460105</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>220000</v>
+        <v>218000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 226,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 220,000원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300016484088297</v>
+        <v>0.2300012304364403</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177166530673166</v>
+        <v>0.05177176763748253</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882056843497378</v>
+        <v>0.02882054692080499</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.9</v>
+        <v>27.64</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.06</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 55519억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 55516억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 56977억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 56970억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59925억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59918억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63235억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63228억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 67215억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 67208억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71372억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 71365억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 55519억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 55516억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 56977억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 56970억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59925억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59918억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63235억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63228억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 67215억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 67208억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71372억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 71365억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.228974561</v>
+        <v>0.228923693</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.170089093</v>
+        <v>0.16993613</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.138519256</v>
+        <v>0.138380753</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.153522814</v>
+        <v>0.153394168</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.210675276</v>
+        <v>0.210602639</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.252644813</v>
+        <v>0.252695927</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154242</v>
+        <v>0.173154272</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155098</v>
+        <v>0.173155483</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173155193</v>
+        <v>0.173155101</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173155362</v>
+        <v>0.173154623</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155274</v>
+        <v>0.173155146</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155045</v>
+        <v>0.173155073</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.003771182</v>
+        <v>-0.005400648</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.004227551</v>
+        <v>0.002428809</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.002152311</v>
+        <v>-0.004136964</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.9283826</v>
+        <v>1770.926242219</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.007858850000000001</v>
+        <v>-0.008424414999999999</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>-0.004243831</v>
+        <v>0.000129378</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>0.006637913</v>
+        <v>-0.009893094999999999</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.91659179</v>
+        <v>1770.919194507</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>0.005997418</v>
+        <v>-0.004373667</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.005968823</v>
+        <v>0.000518975</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.003771182</v>
+        <v>-0.005400648</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.004227551</v>
+        <v>0.002428809</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.002152311</v>
+        <v>-0.004136964</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.9283826</v>
+        <v>1770.926242219</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.007858850000000001</v>
+        <v>-0.008424414999999999</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>-0.004243831</v>
+        <v>0.000129378</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>0.006637913</v>
+        <v>-0.009893094999999999</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.91659179</v>
+        <v>1770.919194507</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>0.005997418</v>
+        <v>-0.004373667</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.005968823</v>
+        <v>0.000518975</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134288046</v>
+        <v>0.134282531</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.122028892</v>
+        <v>0.122013684</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.114733889</v>
+        <v>0.114723002</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.063188153</v>
+        <v>-0.063201596</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122826763</v>
+        <v>0.122820576</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.116460105</v>
+        <v>0.116454613</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300012304364403</v>
+        <v>0.230002233156757</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177176763748253</v>
+        <v>0.05177168289532724</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882054692080499</v>
+        <v>0.02881997858445603</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>218000</v>
+        <v>221000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>226900</v>
+        <v>225916.7</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>218000</v>
+        <v>221000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.64</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.96</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 55516억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 55510억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 56970억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 56938억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59918억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59885억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63228억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63192억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 67208억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 67174억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71365억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 71332억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 55516억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 55510억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 56970억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 56938억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59918억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59885억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63228억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63192억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 67208억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 67174억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71365억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 71332억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2040,25 +2040,25 @@
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9230억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10289억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9640억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9638억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10824억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10821억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2100,25 +2100,25 @@
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9230억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10289억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9640억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9638억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10824억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10821억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4202,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.3, "op_wape_pct": 4.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": "undetermined", "decision": "undetermined", "note": "동결 2024Q2 이전 실적 1분기(&lt;8) 또는 이후 실측 4분기 → OOS 비교 불가(undetermined), 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5231.84, "rev_act": 5131.76, "op_pred": 894.32, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5239.22, "rev_act": 5162.05, "op_pred": 895.58, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5317.65, "rev_act": 5746.09, "op_pred": 908.98, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5245.04, "rev_act": 5804.14, "op_pred": 896.57, "op_act": 976.25}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 5.3, "op_wape_pct": 4.2, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "customer_yard_revenue_weighted", "selection_oos_at_freeze": {"freeze": "2024Q2", "n": 4, "wape_link": null, "wape_trend": null, "adopted": "undetermined", "decision": "undetermined", "note": "동결 2024Q2 이전 실적 1분기(&lt;8) 또는 이후 실측 4분기 → OOS 비교 불가(undetermined), 유의성 조건만으로 채택"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 5231.84, "rev_act": 5131.76, "op_pred": 894.32, "op_act": 935.96}, {"q": "2025Q4", "rev_pred": 5239.23, "rev_act": 5162.05, "op_pred": 895.58, "op_act": 905.28}, {"q": "2026Q1", "rev_pred": 5317.65, "rev_act": 5746.09, "op_pred": 908.99, "op_act": 933.94}, {"q": "2026Q2", "rev_pred": 5245.03, "rev_act": 5804.14, "op_pred": 896.57, "op_act": 976.25}]}</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>221000</v>
+        <v>226000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>213500</v>
+        <v>212500</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>225916.7</v>
+        <v>225357.1</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.228923693</v>
+        <v>0.228790385</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.16993613</v>
+        <v>0.169281966</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.138380753</v>
+        <v>0.137745447</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.153394168</v>
+        <v>0.152736482</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.210602639</v>
+        <v>0.210105889</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.252695927</v>
+        <v>0.252806682</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154272</v>
+        <v>0.1731545</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155483</v>
+        <v>0.173154938</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173155101</v>
+        <v>0.173155195</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173154623</v>
+        <v>0.173155608</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155146</v>
+        <v>0.173155368</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155073</v>
+        <v>0.173155537</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.005400648</v>
+        <v>-0.005273056</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.002428809</v>
+        <v>0.00258669</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.004136964</v>
+        <v>-0.003946904</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.926242219</v>
+        <v>1770.926475464</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.008424414999999999</v>
+        <v>-0.008338569000000001</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>0.000129378</v>
+        <v>-0.009190603</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>-0.009893094999999999</v>
+        <v>0.004733472</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.919194507</v>
+        <v>1770.922265675</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.004373667</v>
+        <v>0.000603265</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>0.000518975</v>
+        <v>-0.004683931</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.005400648</v>
+        <v>-0.005273056</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.002428809</v>
+        <v>0.00258669</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.004136964</v>
+        <v>-0.003946904</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.926242219</v>
+        <v>1770.926475464</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.008424414999999999</v>
+        <v>-0.008338569000000001</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>0.000129378</v>
+        <v>-0.009190603</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>-0.009893094999999999</v>
+        <v>0.004733472</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.919194507</v>
+        <v>1770.922265675</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.004373667</v>
+        <v>0.000603265</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>0.000518975</v>
+        <v>-0.004683931</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134282531</v>
+        <v>0.134268744</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.122013684</v>
+        <v>0.12194953</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.114723002</v>
+        <v>0.114670287</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.063201596</v>
+        <v>-0.063269228</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122820576</v>
+        <v>0.122781515</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.116454613</v>
+        <v>0.116427982</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>221000</v>
+        <v>226000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 220,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 219,500원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.230002233156757</v>
+        <v>0.2300024161673508</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177168289532724</v>
+        <v>0.0517716665564884</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02881997858445603</v>
+        <v>0.02882027709879875</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.03</v>
+        <v>28.66</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.11</v>
+        <v>11.36</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -687,31 +687,31 @@
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 56938억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 56969억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59885억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59916억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63192억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63222억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 67174억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 67202억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71332억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 71359억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1674,31 +1674,31 @@
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 56938억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 56969억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59885억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59916억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63192억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63222억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 67174억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 67202억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71332억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 71359억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2040,25 +2040,25 @@
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9230억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10289억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9638억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10821억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2100,25 +2100,25 @@
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9230억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10289억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9638억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10821억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>226000</v>
+        <v>220500</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>225357.1</v>
+        <v>224750</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.228790385</v>
+        <v>0.22877109</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.169281966</v>
+        <v>0.169927993</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.137745447</v>
+        <v>0.1383386</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.152736482</v>
+        <v>0.153282867</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.210105889</v>
+        <v>0.210643069</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.252806682</v>
+        <v>0.252596147</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.1731545</v>
+        <v>0.173154364</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173154938</v>
+        <v>0.173155296</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173155195</v>
+        <v>0.1731549</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173155608</v>
+        <v>0.17315504</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155368</v>
+        <v>0.173155538</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155537</v>
+        <v>0.173155635</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.005273056</v>
+        <v>-0.00419878</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.00258669</v>
+        <v>0.003755719</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.003946904</v>
+        <v>-0.002672736</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.926475464</v>
+        <v>1770.92782165</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.008338569000000001</v>
+        <v>-0.012402979</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>-0.009190603</v>
+        <v>0.003390182</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>0.004733472</v>
+        <v>0.002701825</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.922265675</v>
+        <v>1770.92011337</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>0.000603265</v>
+        <v>-0.004059379</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.004683931</v>
+        <v>0.000450722</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.005273056</v>
+        <v>-0.00419878</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.00258669</v>
+        <v>0.003755719</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.003946904</v>
+        <v>-0.002672736</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.926475464</v>
+        <v>1770.92782165</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.008338569000000001</v>
+        <v>-0.012402979</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>-0.009190603</v>
+        <v>0.003390182</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>0.004733472</v>
+        <v>0.002701825</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.922265675</v>
+        <v>1770.92011337</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>0.000603265</v>
+        <v>-0.004059379</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.004683931</v>
+        <v>0.000450722</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134268744</v>
+        <v>0.134265987</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.12194953</v>
+        <v>0.122015464</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.114670287</v>
+        <v>0.11472016</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.063269228</v>
+        <v>-0.063213269</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122781515</v>
+        <v>0.122813642</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.116427982</v>
+        <v>0.116448431</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>226000</v>
+        <v>220500</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 219,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 220,500원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300024161673508</v>
+        <v>0.2300014964362788</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.0517716665564884</v>
+        <v>0.05177171368669529</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882027709879875</v>
+        <v>0.02882040056762839</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.66</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.36</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 55510억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 55808억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 56969억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 57170억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59916억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59931억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63222억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63093억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 67202억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 66965억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71359억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 71051억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 55510억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 55808억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 56969억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 57170억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59916억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59931억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63222억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63093억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 67202억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 66965억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71359억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 71051억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2034,31 +2034,31 @@
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8227억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8232억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9239억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10298억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9646억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10826억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2094,31 +2094,31 @@
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8227억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8232억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9231억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9239억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10290억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10298억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9639억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9646억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10823억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10826억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>220500</v>
+        <v>213000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>212500</v>
+        <v>202500</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>224750</v>
+        <v>221500</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.22877109</v>
+        <v>0.235369852</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.169927993</v>
+        <v>0.17405313</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.1383386</v>
+        <v>0.138624638</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.153282867</v>
+        <v>0.150925314</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.210643069</v>
+        <v>0.199926735</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.252596147</v>
+        <v>0.242800613</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173154364</v>
+        <v>0.173155207</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155296</v>
+        <v>0.173155367</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.1731549</v>
+        <v>0.173155033</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.17315504</v>
+        <v>0.173155563</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173155538</v>
+        <v>0.173154656</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155635</v>
+        <v>0.173155548</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.00419878</v>
+        <v>-0.004256194</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.003755719</v>
+        <v>0.003673732</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.002672736</v>
+        <v>-0.002780522</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.92782165</v>
+        <v>1770.92767452</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.012402979</v>
+        <v>-0.002105948</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>0.003390182</v>
+        <v>0.001389185</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>0.002701825</v>
+        <v>-0.006669915</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.92011337</v>
+        <v>1770.926929058</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.004059379</v>
+        <v>-0.003902536</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>0.000450722</v>
+        <v>-0.004902392</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.00419878</v>
+        <v>-0.004256194</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.003755719</v>
+        <v>0.003673732</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.002672736</v>
+        <v>-0.002780522</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.92782165</v>
+        <v>1770.92767452</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.012402979</v>
+        <v>-0.002105948</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>0.003390182</v>
+        <v>0.001389185</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>0.002701825</v>
+        <v>-0.006669915</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.92011337</v>
+        <v>1770.926929058</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.004059379</v>
+        <v>-0.003902536</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>0.000450722</v>
+        <v>-0.004902392</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134265987</v>
+        <v>0.134958101</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.122015464</v>
+        <v>0.122354079</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.11472016</v>
+        <v>0.114649164</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.063213269</v>
+        <v>-0.06336651</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122813642</v>
+        <v>0.122319074</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.116448431</v>
+        <v>0.115942471</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>220500</v>
+        <v>213000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 220,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 216,000원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300014964362788</v>
+        <v>0.2300012460756216</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177171368669529</v>
+        <v>0.05177171985778973</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882040056762839</v>
+        <v>0.02882010306043618</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.96</v>
+        <v>27.01</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.08</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/443060_model.xlsx
+++ b/argus/kship/models/443060_model.xlsx
@@ -681,37 +681,37 @@
     <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 55808억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 56039억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="V21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 57170억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 57364억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="X21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 59931억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 59983억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Y21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 63093억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 63035억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="Z21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 66965억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 66824억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="AA21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-고객 매출 가중지수(t−3) 71051억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
+고객 매출 가중지수(t−3) 70855억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)</t>
       </text>
     </comment>
     <comment ref="P22" authorId="0" shapeId="0">
@@ -1668,37 +1668,37 @@
     </comment>
     <comment ref="U5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 55808억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 56039억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="V5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 57170억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 57364억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="X5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 59931억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 59983억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Y5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 63093억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 63035억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="Z5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 66965억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 66824억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AA5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 고객 매출 가중지수(t−3) 71051억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
+        <t>추정: 고객 매출 가중지수(t−3) 70855억 × 비례계수 0.1262(원점회귀; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.90, n=9, 창 12)
 [yoy]</t>
       </text>
     </comment>
@@ -2034,31 +2034,31 @@
     </comment>
     <comment ref="V11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8232억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 8236억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="X11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9239억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9246억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Y11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10298억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10307억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="Z11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9646억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 9653억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AA11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10826억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(최근 4분기(2025Q3~2026Q2) 잔차 중위) (항등식); 이자손익 = 이자발생자산 10831억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
@@ -2094,31 +2094,31 @@
     </comment>
     <comment ref="V12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 8232억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 8236억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="X12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9239억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9246억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Y12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10298억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10307억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="Z12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 9646억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 9653억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AA12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 10826억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
+        <t>추정: 이자발생자산 10831억 × 2.88%(주석 이자수익 ÷ 평균 이자발생자산(2025Q3~2026Q2)) − 총차입금 0억 × 0.00%(없음) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3994,7 +3994,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4647,35 +4647,35 @@
         <v>1418.75</v>
       </c>
       <c r="Q6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="S6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W6" s="11" t="n"/>
       <c r="X6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AA6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB6" s="11" t="n"/>
     </row>
@@ -4727,35 +4727,35 @@
         <v>1355.4</v>
       </c>
       <c r="Q7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="S7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="T7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="U7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="V7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="W7" s="11" t="n"/>
       <c r="X7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Y7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="Z7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AA7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AB7" s="11" t="n"/>
     </row>
@@ -4807,35 +4807,35 @@
         <v>890.41</v>
       </c>
       <c r="Q8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="S8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W8" s="11" t="n"/>
       <c r="X8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AA8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB8" s="11" t="n"/>
     </row>
@@ -4887,35 +4887,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="Q9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="S9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="T9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="U9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="V9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="W9" s="11" t="n"/>
       <c r="X9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Y9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="Z9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AA9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AB9" s="11" t="n"/>
     </row>
@@ -4967,35 +4967,35 @@
         <v>1631.97</v>
       </c>
       <c r="Q10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="S10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W10" s="11" t="n"/>
       <c r="X10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AA10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB10" s="11" t="n"/>
     </row>
@@ -5047,35 +5047,35 @@
         <v>1539.06</v>
       </c>
       <c r="Q11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="S11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="T11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="U11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="V11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="W11" s="11" t="n"/>
       <c r="X11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Y11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="Z11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AA11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AB11" s="11" t="n"/>
     </row>
@@ -5127,35 +5127,35 @@
         <v>210.43</v>
       </c>
       <c r="Q12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="S12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W12" s="11" t="n"/>
       <c r="X12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AA12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB12" s="11" t="n"/>
     </row>
@@ -5207,35 +5207,35 @@
         <v>202.16</v>
       </c>
       <c r="Q13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="S13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="T13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="U13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="V13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="W13" s="11" t="n"/>
       <c r="X13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Y13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="Z13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AA13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AB13" s="11" t="n"/>
     </row>
@@ -5306,7 +5306,7 @@
         <v>237500</v>
       </c>
       <c r="Q15" s="20" t="n">
-        <v>213000</v>
+        <v>168000</v>
       </c>
       <c r="R15" s="11" t="n"/>
       <c r="S15" s="10" t="n"/>
@@ -5422,7 +5422,7 @@
         <v>175000</v>
       </c>
       <c r="Q17" s="20" t="n">
-        <v>202500</v>
+        <v>158600</v>
       </c>
       <c r="R17" s="11" t="n"/>
       <c r="S17" s="10" t="n"/>
@@ -5480,7 +5480,7 @@
         <v>209638.7</v>
       </c>
       <c r="Q18" s="20" t="n">
-        <v>221500</v>
+        <v>213018.8</v>
       </c>
       <c r="R18" s="11" t="n"/>
       <c r="S18" s="10" t="n"/>
@@ -5596,23 +5596,23 @@
         <v>0.191940847</v>
       </c>
       <c r="U21" s="24" t="n">
-        <v>0.235369852</v>
+        <v>0.240489943</v>
       </c>
       <c r="V21" s="24" t="n">
-        <v>0.17405313</v>
+        <v>0.178038322</v>
       </c>
       <c r="W21" s="25" t="n"/>
       <c r="X21" s="24" t="n">
-        <v>0.138624638</v>
+        <v>0.139613728</v>
       </c>
       <c r="Y21" s="24" t="n">
-        <v>0.150925314</v>
+        <v>0.149867234</v>
       </c>
       <c r="Z21" s="24" t="n">
-        <v>0.199926735</v>
+        <v>0.192461384</v>
       </c>
       <c r="AA21" s="24" t="n">
-        <v>0.242800613</v>
+        <v>0.235183042</v>
       </c>
       <c r="AB21" s="25" t="n"/>
     </row>
@@ -5806,26 +5806,26 @@
         <v>0.173155117</v>
       </c>
       <c r="U23" s="24" t="n">
-        <v>0.173155207</v>
+        <v>0.173154584</v>
       </c>
       <c r="V23" s="24" t="n">
-        <v>0.173155367</v>
+        <v>0.173155288</v>
       </c>
       <c r="W23" s="25">
         <f>IFERROR(subQ!W9/subQ!W5,"")</f>
         <v/>
       </c>
       <c r="X23" s="24" t="n">
-        <v>0.173155033</v>
+        <v>0.173155347</v>
       </c>
       <c r="Y23" s="24" t="n">
-        <v>0.173155563</v>
+        <v>0.173155248</v>
       </c>
       <c r="Z23" s="24" t="n">
-        <v>0.173154656</v>
+        <v>0.173155481</v>
       </c>
       <c r="AA23" s="24" t="n">
-        <v>0.173155548</v>
+        <v>0.1731554</v>
       </c>
       <c r="AB23" s="25">
         <f>IFERROR(subQ!AB9/subQ!AB5,"")</f>
@@ -6710,36 +6710,36 @@
         <v/>
       </c>
       <c r="P32" s="30" t="n">
-        <v>-0.004256194</v>
+        <v>-0.00479287</v>
       </c>
       <c r="Q32" s="30" t="n">
-        <v>0.003673732</v>
+        <v>0.003075121</v>
       </c>
       <c r="R32" s="31" t="n"/>
       <c r="S32" s="30" t="n">
-        <v>-0.002780522</v>
+        <v>-0.003446762</v>
       </c>
       <c r="T32" s="30" t="n">
-        <v>1770.92767452</v>
+        <v>1770.926945739</v>
       </c>
       <c r="U32" s="30" t="n">
-        <v>-0.002105948</v>
+        <v>-0.004307238</v>
       </c>
       <c r="V32" s="30" t="n">
-        <v>0.001389185</v>
+        <v>-0.002984224</v>
       </c>
       <c r="W32" s="31" t="n"/>
       <c r="X32" s="30" t="n">
-        <v>-0.006669915</v>
+        <v>0.000145303</v>
       </c>
       <c r="Y32" s="30" t="n">
-        <v>1770.926929058</v>
+        <v>1770.913013729</v>
       </c>
       <c r="Z32" s="30" t="n">
-        <v>-0.003902536</v>
+        <v>0.001044287</v>
       </c>
       <c r="AA32" s="30" t="n">
-        <v>-0.004902392</v>
+        <v>0.005336578</v>
       </c>
       <c r="AB32" s="31" t="n"/>
     </row>
@@ -6795,36 +6795,36 @@
         <v/>
       </c>
       <c r="P33" s="30" t="n">
-        <v>-0.004256194</v>
+        <v>-0.00479287</v>
       </c>
       <c r="Q33" s="30" t="n">
-        <v>0.003673732</v>
+        <v>0.003075121</v>
       </c>
       <c r="R33" s="31" t="n"/>
       <c r="S33" s="30" t="n">
-        <v>-0.002780522</v>
+        <v>-0.003446762</v>
       </c>
       <c r="T33" s="30" t="n">
-        <v>1770.92767452</v>
+        <v>1770.926945739</v>
       </c>
       <c r="U33" s="30" t="n">
-        <v>-0.002105948</v>
+        <v>-0.004307238</v>
       </c>
       <c r="V33" s="30" t="n">
-        <v>0.001389185</v>
+        <v>-0.002984224</v>
       </c>
       <c r="W33" s="31" t="n"/>
       <c r="X33" s="30" t="n">
-        <v>-0.006669915</v>
+        <v>0.000145303</v>
       </c>
       <c r="Y33" s="30" t="n">
-        <v>1770.926929058</v>
+        <v>1770.913013729</v>
       </c>
       <c r="Z33" s="30" t="n">
-        <v>-0.003902536</v>
+        <v>0.001044287</v>
       </c>
       <c r="AA33" s="30" t="n">
-        <v>-0.004902392</v>
+        <v>0.005336578</v>
       </c>
       <c r="AB33" s="31" t="n"/>
     </row>
@@ -7023,23 +7023,23 @@
         <v>-0.099812966</v>
       </c>
       <c r="U36" s="24" t="n">
-        <v>0.134958101</v>
+        <v>0.13549442</v>
       </c>
       <c r="V36" s="24" t="n">
-        <v>0.122354079</v>
+        <v>0.122695759</v>
       </c>
       <c r="W36" s="25" t="n"/>
       <c r="X36" s="24" t="n">
-        <v>0.114649164</v>
+        <v>0.114658554</v>
       </c>
       <c r="Y36" s="24" t="n">
-        <v>-0.06336651</v>
+        <v>-0.063407005</v>
       </c>
       <c r="Z36" s="24" t="n">
-        <v>0.122319074</v>
+        <v>0.121986972</v>
       </c>
       <c r="AA36" s="24" t="n">
-        <v>0.115942471</v>
+        <v>0.115589767</v>
       </c>
       <c r="AB36" s="25" t="n"/>
     </row>
@@ -7472,11 +7472,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>213000</v>
+        <v>168000</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 216,000원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 201,500원)</t>
         </is>
       </c>
       <c r="H44" s="9" t="n"/>
@@ -7509,7 +7509,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="D51" s="36" t="n">
-        <v>0.2300012460756216</v>
+        <v>0.2300014813858174</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.05177171985778973</v>
+        <v>0.05177170588788548</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.02882010306043618</v>
+        <v>0.02881982366071963</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -23461,7 +23461,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -27070,7 +27070,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -28762,7 +28762,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.01</v>
+        <v>21.3</v>
       </c>
     </row>
     <row r="32">
@@ -28772,7 +28772,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.7</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="33">
